--- a/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,03</t>
+          <t>0,88; 5,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,49</t>
+          <t>1,91; 6,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,8</t>
+          <t>7,45; 13,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,77</t>
+          <t>0,13; 5,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,66</t>
+          <t>-0,49; 4,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,92</t>
+          <t>2,54; 7,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,63</t>
+          <t>1,35; 4,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,01</t>
+          <t>1,37; 4,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,68</t>
+          <t>5,5; 9,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 253,93</t>
+          <t>12,76; 260,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,0; 321,12</t>
+          <t>50,13; 335,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>197,42; 624,04</t>
+          <t>190,07; 636,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 155,34</t>
+          <t>-0,23; 143,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 123,07</t>
+          <t>-8,53; 124,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 201,91</t>
+          <t>39,14; 203,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,11; 143,87</t>
+          <t>27,92; 151,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,74; 155,46</t>
+          <t>26,08; 157,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>123,07; 304,73</t>
+          <t>116,58; 303,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,12</t>
+          <t>0,38; 5,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,59</t>
+          <t>-2,71; 1,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,54</t>
+          <t>-1,06; 7,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,69</t>
+          <t>1,58; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,05</t>
+          <t>-1,11; 3,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,94</t>
+          <t>5,18; 9,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,15</t>
+          <t>1,7; 5,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,08</t>
+          <t>-1,14; 2,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,88</t>
+          <t>1,15; 7,77</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 118,89</t>
+          <t>3,86; 113,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 38,17</t>
+          <t>-40,13; 32,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 155,7</t>
+          <t>-15,25; 151,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,41; 140,89</t>
+          <t>20,63; 137,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 86,79</t>
+          <t>-16,54; 80,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,14; 211,78</t>
+          <t>70,32; 208,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,62; 102,06</t>
+          <t>25,56; 103,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 42,23</t>
+          <t>-18,03; 43,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,71; 158,98</t>
+          <t>34,29; 151,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,46</t>
+          <t>-1,08; 4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,66</t>
+          <t>-5,04; -0,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,04</t>
+          <t>3,5; 9,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,3</t>
+          <t>-0,12; 5,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,63</t>
+          <t>-3,17; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 55,06</t>
+          <t>4,42; 58,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,09</t>
+          <t>0,04; 3,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,09</t>
+          <t>-3,49; 0,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 42,57</t>
+          <t>5,43; 42,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 98,83</t>
+          <t>-14,41; 105,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,62; -10,89</t>
+          <t>-68,8; -7,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,58; 218,34</t>
+          <t>45,11; 212,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 113,57</t>
+          <t>-5,14; 103,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 35,98</t>
+          <t>-45,43; 34,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,22; 1227,33</t>
+          <t>71,2; 1216,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 82,47</t>
+          <t>-0,33; 79,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 0,28</t>
+          <t>-49,6; 1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,56; 815,7</t>
+          <t>88,36; 924,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,53</t>
+          <t>-0,39; 4,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,75</t>
+          <t>-0,54; 3,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,78</t>
+          <t>0,64; 4,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,45</t>
+          <t>-0,63; 4,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,58</t>
+          <t>-2,53; 2,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,98</t>
+          <t>-2,01; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,72</t>
+          <t>0,26; 3,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,34</t>
+          <t>-1,01; 2,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,12</t>
+          <t>0,01; 3,24</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 103,25</t>
+          <t>-7,34; 102,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 84,82</t>
+          <t>-9,03; 79,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 106,03</t>
+          <t>8,8; 105,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 67,42</t>
+          <t>-8,15; 64,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 39,17</t>
+          <t>-28,99; 37,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 46,15</t>
+          <t>-22,55; 45,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 59,92</t>
+          <t>3,6; 63,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 38,3</t>
+          <t>-12,89; 39,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 51,88</t>
+          <t>0,02; 53,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,57</t>
+          <t>1,02; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,64</t>
+          <t>-0,78; 1,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,96</t>
+          <t>3,22; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,12</t>
+          <t>1,48; 4,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,8</t>
+          <t>-0,58; 1,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 25,27</t>
+          <t>4,22; 24,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,41</t>
+          <t>1,74; 3,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,41</t>
+          <t>-0,29; 1,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 17,2</t>
+          <t>4,66; 15,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21,43; 79,23</t>
+          <t>17,2; 76,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 37,67</t>
+          <t>-13,72; 36,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58,69; 154,49</t>
+          <t>62,04; 154,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,25; 73,1</t>
+          <t>20,45; 73,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 31,97</t>
+          <t>-8,84; 33,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,01; 422,49</t>
+          <t>66,08; 418,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,21; 66,27</t>
+          <t>28,35; 67,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 27,01</t>
+          <t>-4,87; 27,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>79,18; 323,21</t>
+          <t>80,62; 298,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>7,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,23</t>
+          <t>0,82; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,64</t>
+          <t>1,79; 6,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,14</t>
+          <t>6,8; 12,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,83</t>
+          <t>0,52; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,89</t>
+          <t>-0,42; 4,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,84</t>
+          <t>3,46; 8,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,86</t>
+          <t>1,31; 4,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,98</t>
+          <t>1,45; 4,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,57</t>
+          <t>5,84; 9,57</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>355,69%</t>
+          <t>341,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>109,5%</t>
+          <t>121,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>196,55%</t>
+          <t>200,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 260,35</t>
+          <t>20,59; 268,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,13; 335,09</t>
+          <t>42,19; 309,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>190,07; 636,28</t>
+          <t>172,41; 630,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 143,51</t>
+          <t>4,65; 156,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 124,72</t>
+          <t>-7,82; 119,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,14; 203,93</t>
+          <t>51,39; 228,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,92; 151,77</t>
+          <t>24,87; 149,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,08; 157,92</t>
+          <t>31,8; 154,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116,58; 303,37</t>
+          <t>116,75; 288,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>6,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,12</t>
+          <t>0,42; 4,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,47</t>
+          <t>-2,55; 1,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,73</t>
+          <t>3,66; 9,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,51</t>
+          <t>1,56; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,75</t>
+          <t>-0,95; 3,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,85</t>
+          <t>5,22; 9,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,02</t>
+          <t>1,64; 5,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,15</t>
+          <t>-1,05; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,77</t>
+          <t>5,29; 8,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>114,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>132,93%</t>
+          <t>131,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101,75%</t>
+          <t>123,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 113,71</t>
+          <t>5,71; 106,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 32,67</t>
+          <t>-39,44; 36,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 151,06</t>
+          <t>54,06; 205,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,63; 137,34</t>
+          <t>20,48; 138,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 80,33</t>
+          <t>-13,67; 75,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 208,55</t>
+          <t>67,84; 216,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 103,08</t>
+          <t>26,04; 108,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 43,26</t>
+          <t>-15,85; 42,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,29; 151,27</t>
+          <t>80,89; 182,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,07</t>
+          <t>6,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,51</t>
+          <t>-0,9; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,46</t>
+          <t>-5,09; -0,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,95</t>
+          <t>3,03; 9,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,26</t>
+          <t>-0,47; 5,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,68</t>
+          <t>-3,3; 1,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 58,87</t>
+          <t>3,76; 9,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,9</t>
+          <t>0,18; 3,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,04</t>
+          <t>-3,36; 0,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 42,05</t>
+          <t>4,1; 8,14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117,27%</t>
+          <t>106,23%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>417,91%</t>
+          <t>106,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>290,66%</t>
+          <t>106,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 105,19</t>
+          <t>-13,87; 100,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,8; -7,48</t>
+          <t>-68,8; -7,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,11; 212,09</t>
+          <t>35,9; 205,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 103,01</t>
+          <t>-7,13; 110,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 34,39</t>
+          <t>-46,43; 34,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,2; 1216,83</t>
+          <t>48,13; 196,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 79,42</t>
+          <t>1,92; 80,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 1,6</t>
+          <t>-49,54; 2,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,36; 924,33</t>
+          <t>57,89; 162,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,62</t>
+          <t>-0,41; 4,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,58</t>
+          <t>-0,71; 3,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,82</t>
+          <t>0,06; 4,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,38</t>
+          <t>-0,69; 4,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,44</t>
+          <t>-2,53; 2,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,09</t>
+          <t>-0,92; 3,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,69</t>
+          <t>0,22; 3,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,35</t>
+          <t>-0,77; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,24</t>
+          <t>0,35; 3,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 102,37</t>
+          <t>-7,0; 96,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 79,59</t>
+          <t>-12,47; 83,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 105,26</t>
+          <t>-1,24; 104,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 64,68</t>
+          <t>-8,21; 64,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 37,89</t>
+          <t>-27,13; 38,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 45,88</t>
+          <t>-10,04; 59,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 63,15</t>
+          <t>3,22; 61,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 39,88</t>
+          <t>-10,44; 40,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 53,06</t>
+          <t>4,74; 59,17</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,39</t>
+          <t>1,17; 3,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,62</t>
+          <t>-0,53; 1,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,95</t>
+          <t>4,52; 7,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,19</t>
+          <t>1,4; 4,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,92</t>
+          <t>-0,68; 1,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,02</t>
+          <t>3,92; 6,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,56</t>
+          <t>1,69; 3,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,46</t>
+          <t>-0,17; 1,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 15,84</t>
+          <t>4,63; 6,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109,53%</t>
+          <t>117,5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>151,36%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>134,04%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,2; 76,62</t>
+          <t>20,1; 77,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 36,56</t>
+          <t>-9,85; 36,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62,04; 154,33</t>
+          <t>80,42; 164,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,45; 73,41</t>
+          <t>20,11; 71,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 33,54</t>
+          <t>-10,08; 29,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,08; 418,22</t>
+          <t>56,55; 112,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,35; 67,2</t>
+          <t>27,45; 65,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 27,8</t>
+          <t>-2,75; 27,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>80,62; 298,72</t>
+          <t>77,09; 121,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
